--- a/psdash/demo/weights_table.xlsx
+++ b/psdash/demo/weights_table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
   <si>
     <t>Weight Diagnostics</t>
   </si>
@@ -21,9 +21,15 @@
     <t>Metric</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Treatment</t>
   </si>
   <si>
+    <t>statin</t>
+  </si>
+  <si>
     <t>Total N</t>
   </si>
   <si>
@@ -76,76 +82,120 @@
   </si>
   <si>
     <t>p95</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>statin</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>551</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>1.9964</t>
-  </si>
-  <si>
-    <t>1.2713</t>
-  </si>
-  <si>
-    <t>1.0520</t>
-  </si>
-  <si>
-    <t>12.6015</t>
-  </si>
-  <si>
-    <t>0.637</t>
-  </si>
-  <si>
-    <t>569.4</t>
-  </si>
-  <si>
-    <t>71.2</t>
-  </si>
-  <si>
-    <t>95.0</t>
-  </si>
-  <si>
-    <t>78.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1.0832</t>
-  </si>
-  <si>
-    <t>1.1272</t>
-  </si>
-  <si>
-    <t>4.5418</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+  <fonts count="27">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -159,7 +209,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -167,12 +217,269 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,175 +491,180 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="32.7109375" style="24" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="25" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="7">
+        <v>551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B6" s="8">
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="9">
+        <v>1.9964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1.2713000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="B9" s="11">
+        <v>1.052</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="B10" s="12">
+        <v>12.6015</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
+        <v>12</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.63700000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="B12" s="14">
+        <v>569.39999999999998</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
+        <v>14</v>
+      </c>
+      <c r="B13" s="15">
+        <v>71.200000000000003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="B14" s="16">
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="B15" s="17">
+        <v>78.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="B16" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="B17" s="19">
+        <v>0.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="B18" s="20">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
+        <v>20</v>
+      </c>
+      <c r="B19" s="21">
+        <v>1.0831999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
+        <v>21</v>
+      </c>
+      <c r="B20" s="22">
+        <v>1.1272</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>22</v>
+      </c>
+      <c r="B21" s="23">
+        <v>4.5418000000000003</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
 </worksheet>
 </file>